--- a/PO_TBD_20260618.xlsx
+++ b/PO_TBD_20260618.xlsx
@@ -616,7 +616,7 @@
       </c>
       <c r="B10" s="6" t="inlineStr">
         <is>
-          <t>TAB MUCOSOLVAN (AMBROXOL) 30MG DKSH</t>
+          <t>TAB ZITHROMAX (AZITHROMYCIN) 250MG 6'S PFIZER</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
@@ -626,20 +626,20 @@
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>TABLET</t>
+          <t>PACKET</t>
         </is>
       </c>
       <c r="E10" s="5" t="n">
         <v>0</v>
       </c>
       <c r="F10" s="5" t="n">
-        <v>100</v>
+        <v>60</v>
       </c>
       <c r="G10" s="7" t="n">
-        <v>0.46</v>
+        <v>42.4</v>
       </c>
       <c r="H10" s="7" t="n">
-        <v>46</v>
+        <v>2544</v>
       </c>
     </row>
     <row r="11">
@@ -648,7 +648,7 @@
       </c>
       <c r="B11" s="9" t="inlineStr">
         <is>
-          <t>SYR SEDILIX-RX LINCTUS (DEXTROMETHORPHAN 15MG/ PROMETHAZINE 3.125MG/ PHENYLEPHRINE 5MG EVERY 5ML)  90ML XEPA</t>
+          <t>TAB MUCOSOLVAN (AMBROXOL) 30MG DKSH</t>
         </is>
       </c>
       <c r="C11" s="8" t="inlineStr">
@@ -658,20 +658,20 @@
       </c>
       <c r="D11" s="8" t="inlineStr">
         <is>
-          <t>BOTTLE</t>
+          <t>TABLET</t>
         </is>
       </c>
       <c r="E11" s="8" t="n">
         <v>0</v>
       </c>
       <c r="F11" s="8" t="n">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="G11" s="10" t="n">
-        <v>5.9</v>
+        <v>0.46</v>
       </c>
       <c r="H11" s="10" t="n">
-        <v>59</v>
+        <v>46</v>
       </c>
     </row>
     <row r="12">
@@ -680,7 +680,7 @@
       </c>
       <c r="B12" s="6" t="inlineStr">
         <is>
-          <t>PROCTOSEDYL OINTMENT (FRAMYCETIN SULPHATE 1% W/W, HYDROCORTISONE 0.5% W/W, CINCHOCAINE.5% W/W, AESCULIN 1% W/W) 15G ZUELLIG PHARMA</t>
+          <t>SYR SEDILIX-RX LINCTUS (DEXTROMETHORPHAN 15MG/ PROMETHAZINE 3.125MG/ PHENYLEPHRINE 5MG EVERY 5ML)  90ML XEPA</t>
         </is>
       </c>
       <c r="C12" s="5" t="inlineStr">
@@ -690,20 +690,20 @@
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>TUBE</t>
+          <t>BOTTLE</t>
         </is>
       </c>
       <c r="E12" s="5" t="n">
         <v>0</v>
       </c>
       <c r="F12" s="5" t="n">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="G12" s="7" t="n">
-        <v>35</v>
+        <v>5.9</v>
       </c>
       <c r="H12" s="7" t="n">
-        <v>1050</v>
+        <v>59</v>
       </c>
     </row>
     <row r="13">
@@ -712,7 +712,7 @@
       </c>
       <c r="B13" s="9" t="inlineStr">
         <is>
-          <t>ORREPASTE (TRIAMCINOLONE ACETONIDE 0.1% W/W) 5G HOE</t>
+          <t>PROCTOSEDYL OINTMENT (FRAMYCETIN SULPHATE 1% W/W, HYDROCORTISONE 0.5% W/W, CINCHOCAINE.5% W/W, AESCULIN 1% W/W) 15G ZUELLIG PHARMA</t>
         </is>
       </c>
       <c r="C13" s="8" t="inlineStr">
@@ -729,13 +729,13 @@
         <v>0</v>
       </c>
       <c r="F13" s="8" t="n">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="G13" s="10" t="n">
-        <v>11.36</v>
+        <v>35</v>
       </c>
       <c r="H13" s="10" t="n">
-        <v>113.6</v>
+        <v>1050</v>
       </c>
     </row>
     <row r="14">
@@ -744,7 +744,7 @@
       </c>
       <c r="B14" s="6" t="inlineStr">
         <is>
-          <t>AXCEL UREA (UREA 10% W/W) CREAM 20G KOTRA PHARMA</t>
+          <t>ORREPASTE (TRIAMCINOLONE ACETONIDE 0.1% W/W) 5G HOE</t>
         </is>
       </c>
       <c r="C14" s="5" t="inlineStr">
@@ -764,10 +764,10 @@
         <v>10</v>
       </c>
       <c r="G14" s="7" t="n">
-        <v>12</v>
+        <v>11.36</v>
       </c>
       <c r="H14" s="7" t="n">
-        <v>120</v>
+        <v>113.6</v>
       </c>
     </row>
     <row r="15">
@@ -776,7 +776,7 @@
       </c>
       <c r="B15" s="9" t="inlineStr">
         <is>
-          <t>INJ HYALGAN ( HYALURONIC ACID ) 20MG/2ML PE PHARMA</t>
+          <t>AXCEL UREA (UREA 10% W/W) CREAM 20G KOTRA PHARMA</t>
         </is>
       </c>
       <c r="C15" s="8" t="inlineStr">
@@ -786,20 +786,20 @@
       </c>
       <c r="D15" s="8" t="inlineStr">
         <is>
-          <t>UNIT</t>
+          <t>TUBE</t>
         </is>
       </c>
       <c r="E15" s="8" t="n">
         <v>0</v>
       </c>
       <c r="F15" s="8" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="G15" s="10" t="n">
-        <v>118</v>
+        <v>12</v>
       </c>
       <c r="H15" s="10" t="n">
-        <v>590</v>
+        <v>120</v>
       </c>
     </row>
     <row r="16">
@@ -808,7 +808,7 @@
       </c>
       <c r="B16" s="6" t="inlineStr">
         <is>
-          <t>SYR BENA EXPECTORANT(DIPHENHYDRAMINE 14MG, AMMONIUM CHLORIDE 135MG/5ML) 90ML XEPA</t>
+          <t>INJ HYALGAN ( HYALURONIC ACID ) 20MG/2ML PE PHARMA</t>
         </is>
       </c>
       <c r="C16" s="5" t="inlineStr">
@@ -818,20 +818,20 @@
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>BOTTLE</t>
+          <t>UNIT</t>
         </is>
       </c>
       <c r="E16" s="5" t="n">
         <v>0</v>
       </c>
       <c r="F16" s="5" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="G16" s="7" t="n">
-        <v>3.4</v>
+        <v>118</v>
       </c>
       <c r="H16" s="7" t="n">
-        <v>34</v>
+        <v>590</v>
       </c>
     </row>
     <row r="17">
@@ -840,7 +840,7 @@
       </c>
       <c r="B17" s="9" t="inlineStr">
         <is>
-          <t>DYFAZINE CREAM (SILVER SULPHADIAZINE 1%) 50G DYNAPHARM</t>
+          <t>SYR BENA EXPECTORANT(DIPHENHYDRAMINE 14MG, AMMONIUM CHLORIDE 135MG/5ML) 90ML XEPA</t>
         </is>
       </c>
       <c r="C17" s="8" t="inlineStr">
@@ -850,7 +850,7 @@
       </c>
       <c r="D17" s="8" t="inlineStr">
         <is>
-          <t>TUBE</t>
+          <t>BOTTLE</t>
         </is>
       </c>
       <c r="E17" s="8" t="n">
@@ -860,10 +860,10 @@
         <v>10</v>
       </c>
       <c r="G17" s="10" t="n">
-        <v>13.64</v>
+        <v>3.4</v>
       </c>
       <c r="H17" s="10" t="n">
-        <v>136.4</v>
+        <v>34</v>
       </c>
     </row>
     <row r="18">
@@ -872,7 +872,7 @@
       </c>
       <c r="B18" s="6" t="inlineStr">
         <is>
-          <t>TAB APROVASC ( IRBESARTAN150MG / AMLODIPINE 5MG) SANOFI</t>
+          <t>DYFAZINE CREAM (SILVER SULPHADIAZINE 1%) 50G DYNAPHARM</t>
         </is>
       </c>
       <c r="C18" s="5" t="inlineStr">
@@ -882,20 +882,20 @@
       </c>
       <c r="D18" s="5" t="inlineStr">
         <is>
-          <t>TABLET</t>
+          <t>TUBE</t>
         </is>
       </c>
       <c r="E18" s="5" t="n">
         <v>0</v>
       </c>
       <c r="F18" s="5" t="n">
-        <v>52</v>
+        <v>10</v>
       </c>
       <c r="G18" s="7" t="n">
-        <v>1.4</v>
+        <v>13.64</v>
       </c>
       <c r="H18" s="7" t="n">
-        <v>72.8</v>
+        <v>136.4</v>
       </c>
     </row>
     <row r="19">
@@ -904,7 +904,7 @@
       </c>
       <c r="B19" s="9" t="inlineStr">
         <is>
-          <t>INJ TACARLINE (ADRENALINE 1MG/ML) 1ML DUOPHARMA</t>
+          <t>TAB APROVASC ( IRBESARTAN150MG / AMLODIPINE 5MG) SANOFI</t>
         </is>
       </c>
       <c r="C19" s="8" t="inlineStr">
@@ -914,20 +914,20 @@
       </c>
       <c r="D19" s="8" t="inlineStr">
         <is>
-          <t>VIAL</t>
+          <t>TABLET</t>
         </is>
       </c>
       <c r="E19" s="8" t="n">
         <v>0</v>
       </c>
       <c r="F19" s="8" t="n">
-        <v>3</v>
+        <v>52</v>
       </c>
       <c r="G19" s="10" t="n">
-        <v>3.18</v>
+        <v>1.4</v>
       </c>
       <c r="H19" s="10" t="n">
-        <v>9.539999999999999</v>
+        <v>72.8</v>
       </c>
     </row>
     <row r="20">
@@ -936,7 +936,7 @@
       </c>
       <c r="B20" s="6" t="inlineStr">
         <is>
-          <t>TAB COAPROVEL  (IRBESARTAN/HYDROCHLOROTHIAZIDE) 300MG/12.5MG SANOFI</t>
+          <t>INJ TACARLINE (ADRENALINE 1MG/ML) 1ML DUOPHARMA</t>
         </is>
       </c>
       <c r="C20" s="5" t="inlineStr">
@@ -946,20 +946,20 @@
       </c>
       <c r="D20" s="5" t="inlineStr">
         <is>
-          <t>TABLET</t>
+          <t>VIAL</t>
         </is>
       </c>
       <c r="E20" s="5" t="n">
         <v>0</v>
       </c>
       <c r="F20" s="5" t="n">
-        <v>52</v>
+        <v>3</v>
       </c>
       <c r="G20" s="7" t="n">
-        <v>2.3</v>
+        <v>3.18</v>
       </c>
       <c r="H20" s="7" t="n">
-        <v>119.6</v>
+        <v>9.539999999999999</v>
       </c>
     </row>
     <row r="21">
@@ -968,7 +968,7 @@
       </c>
       <c r="B21" s="9" t="inlineStr">
         <is>
-          <t>IVD HARTMANN'S SOLUTION 500ML B. BRAUN</t>
+          <t>TAB COAPROVEL  (IRBESARTAN/HYDROCHLOROTHIAZIDE) 300MG/12.5MG SANOFI</t>
         </is>
       </c>
       <c r="C21" s="8" t="inlineStr">
@@ -978,20 +978,20 @@
       </c>
       <c r="D21" s="8" t="inlineStr">
         <is>
-          <t>UNIT</t>
+          <t>TABLET</t>
         </is>
       </c>
       <c r="E21" s="8" t="n">
         <v>0</v>
       </c>
       <c r="F21" s="8" t="n">
-        <v>24</v>
+        <v>52</v>
       </c>
       <c r="G21" s="10" t="n">
-        <v>3.7</v>
+        <v>2.3</v>
       </c>
       <c r="H21" s="10" t="n">
-        <v>88.8</v>
+        <v>119.6</v>
       </c>
     </row>
     <row r="22">
@@ -1000,7 +1000,7 @@
       </c>
       <c r="B22" s="6" t="inlineStr">
         <is>
-          <t>KEZORAL (KETOCONAZOLE 2% W/W) CREAM 15G DUOPHARMA</t>
+          <t>IVD HARTMANN'S SOLUTION 500ML B. BRAUN</t>
         </is>
       </c>
       <c r="C22" s="5" t="inlineStr">
@@ -1010,20 +1010,20 @@
       </c>
       <c r="D22" s="5" t="inlineStr">
         <is>
-          <t>TUBE</t>
+          <t>UNIT</t>
         </is>
       </c>
       <c r="E22" s="5" t="n">
         <v>0</v>
       </c>
       <c r="F22" s="5" t="n">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="G22" s="7" t="n">
-        <v>7.7</v>
+        <v>3.7</v>
       </c>
       <c r="H22" s="7" t="n">
-        <v>92.40000000000001</v>
+        <v>88.8</v>
       </c>
     </row>
     <row r="23">
@@ -1032,7 +1032,7 @@
       </c>
       <c r="B23" s="9" t="inlineStr">
         <is>
-          <t>APPETON MV LYSINE SYRUP 120ML (VITAMIN A 1000IU + VITAMIN D3 200IU + VITAMIN B1 0.5MG + VITAMIN B2 0.5MG + VITAMIN B6 0.5MG + VITAMIN E 5IU + NICOTINAMIDE 6MG + PANTOTHENIC ACID 2MG + LYSINE 80MG) KOTRA PHARMA</t>
+          <t>KEZORAL (KETOCONAZOLE 2% W/W) CREAM 15G DUOPHARMA</t>
         </is>
       </c>
       <c r="C23" s="8" t="inlineStr">
@@ -1042,20 +1042,20 @@
       </c>
       <c r="D23" s="8" t="inlineStr">
         <is>
-          <t>BOTTLE</t>
+          <t>TUBE</t>
         </is>
       </c>
       <c r="E23" s="8" t="n">
         <v>0</v>
       </c>
       <c r="F23" s="8" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="G23" s="10" t="n">
-        <v>39.04</v>
+        <v>7.7</v>
       </c>
       <c r="H23" s="10" t="n">
-        <v>390.4</v>
+        <v>92.40000000000001</v>
       </c>
     </row>
     <row r="24">
@@ -1064,7 +1064,7 @@
       </c>
       <c r="B24" s="6" t="inlineStr">
         <is>
-          <t>SCABOMA LOTION  ( LINDANE 1% ) GLENMARK</t>
+          <t>APPETON MV LYSINE SYRUP 120ML (VITAMIN A 1000IU + VITAMIN D3 200IU + VITAMIN B1 0.5MG + VITAMIN B2 0.5MG + VITAMIN B6 0.5MG + VITAMIN E 5IU + NICOTINAMIDE 6MG + PANTOTHENIC ACID 2MG + LYSINE 80MG) KOTRA PHARMA</t>
         </is>
       </c>
       <c r="C24" s="5" t="inlineStr">
@@ -1084,10 +1084,10 @@
         <v>10</v>
       </c>
       <c r="G24" s="7" t="n">
-        <v>17.5</v>
+        <v>39.04</v>
       </c>
       <c r="H24" s="7" t="n">
-        <v>175</v>
+        <v>390.4</v>
       </c>
     </row>
     <row r="25">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="B25" s="9" t="inlineStr">
         <is>
-          <t>TAB JARDIANCE ( EMPAGLIFLOZIN ) 25MG BOEHRINGER</t>
+          <t>SCABOMA LOTION  ( LINDANE 1% ) GLENMARK</t>
         </is>
       </c>
       <c r="C25" s="8" t="inlineStr">
@@ -1106,20 +1106,20 @@
       </c>
       <c r="D25" s="8" t="inlineStr">
         <is>
-          <t>TABLET</t>
+          <t>BOTTLE</t>
         </is>
       </c>
       <c r="E25" s="8" t="n">
         <v>0</v>
       </c>
       <c r="F25" s="8" t="n">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="G25" s="10" t="n">
-        <v>5.07</v>
+        <v>17.5</v>
       </c>
       <c r="H25" s="10" t="n">
-        <v>152.1</v>
+        <v>175</v>
       </c>
     </row>
     <row r="26">
@@ -1128,7 +1128,7 @@
       </c>
       <c r="B26" s="6" t="inlineStr">
         <is>
-          <t>TABLET METGYL (METRONIDAZOLE) 400MG SM PHARMACEUTICALS</t>
+          <t>TAB JARDIANCE ( EMPAGLIFLOZIN ) 25MG BOEHRINGER</t>
         </is>
       </c>
       <c r="C26" s="5" t="inlineStr">
@@ -1142,16 +1142,16 @@
         </is>
       </c>
       <c r="E26" s="5" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="F26" s="5" t="n">
-        <v>190</v>
+        <v>30</v>
       </c>
       <c r="G26" s="7" t="n">
-        <v>0.09</v>
+        <v>5.07</v>
       </c>
       <c r="H26" s="7" t="n">
-        <v>17.1</v>
+        <v>152.1</v>
       </c>
     </row>
     <row r="27">
@@ -1160,7 +1160,7 @@
       </c>
       <c r="B27" s="9" t="inlineStr">
         <is>
-          <t>INJ MENQUADFI (MENINGOCOCCAL VACCINE) 0.5ML 1D SANOFI</t>
+          <t>TABLET METGYL (METRONIDAZOLE) 400MG SM PHARMACEUTICALS</t>
         </is>
       </c>
       <c r="C27" s="8" t="inlineStr">
@@ -1170,20 +1170,20 @@
       </c>
       <c r="D27" s="8" t="inlineStr">
         <is>
-          <t>DOSE</t>
+          <t>TABLET</t>
         </is>
       </c>
       <c r="E27" s="8" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="F27" s="8" t="n">
-        <v>1</v>
+        <v>190</v>
       </c>
       <c r="G27" s="10" t="n">
-        <v>97</v>
+        <v>0.09</v>
       </c>
       <c r="H27" s="10" t="n">
-        <v>97</v>
+        <v>17.1</v>
       </c>
     </row>
     <row r="28">
@@ -1192,7 +1192,7 @@
       </c>
       <c r="B28" s="6" t="inlineStr">
         <is>
-          <t>TAB EUTHYROX (LEVOTHYROXINE SODIUM) 100MCG MERCK</t>
+          <t>INJ MENQUADFI (MENINGOCOCCAL VACCINE) 0.5ML 1D SANOFI</t>
         </is>
       </c>
       <c r="C28" s="5" t="inlineStr">
@@ -1202,20 +1202,20 @@
       </c>
       <c r="D28" s="5" t="inlineStr">
         <is>
-          <t>TABLET</t>
+          <t>DOSE</t>
         </is>
       </c>
       <c r="E28" s="5" t="n">
         <v>0</v>
       </c>
       <c r="F28" s="5" t="n">
-        <v>100</v>
+        <v>1</v>
       </c>
       <c r="G28" s="7" t="n">
-        <v>0.53</v>
+        <v>97</v>
       </c>
       <c r="H28" s="7" t="n">
-        <v>53</v>
+        <v>97</v>
       </c>
     </row>
     <row r="29">
@@ -1224,7 +1224,7 @@
       </c>
       <c r="B29" s="9" t="inlineStr">
         <is>
-          <t>PNEUMOVAX 23 ( PNEUMOCOCCAL VACCINE POLYVALENT) MSD</t>
+          <t>TAB EUTHYROX (LEVOTHYROXINE SODIUM) 100MCG MERCK</t>
         </is>
       </c>
       <c r="C29" s="8" t="inlineStr">
@@ -1234,20 +1234,20 @@
       </c>
       <c r="D29" s="8" t="inlineStr">
         <is>
-          <t>DOSE</t>
+          <t>TABLET</t>
         </is>
       </c>
       <c r="E29" s="8" t="n">
         <v>0</v>
       </c>
       <c r="F29" s="8" t="n">
-        <v>5</v>
+        <v>100</v>
       </c>
       <c r="G29" s="10" t="n">
-        <v>106.5</v>
+        <v>0.53</v>
       </c>
       <c r="H29" s="10" t="n">
-        <v>532.5</v>
+        <v>53</v>
       </c>
     </row>
     <row r="30">
@@ -1256,7 +1256,7 @@
       </c>
       <c r="B30" s="6" t="inlineStr">
         <is>
-          <t>FIX DERMA MOISTURIZING CREAM FOR DRY SKIN 60G SYNERRV</t>
+          <t>PNEUMOVAX 23 ( PNEUMOCOCCAL VACCINE POLYVALENT) MSD</t>
         </is>
       </c>
       <c r="C30" s="5" t="inlineStr">
@@ -1266,20 +1266,20 @@
       </c>
       <c r="D30" s="5" t="inlineStr">
         <is>
-          <t>TUBE</t>
+          <t>DOSE</t>
         </is>
       </c>
       <c r="E30" s="5" t="n">
         <v>0</v>
       </c>
       <c r="F30" s="5" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="G30" s="7" t="n">
-        <v>0</v>
+        <v>106.5</v>
       </c>
       <c r="H30" s="7" t="n">
-        <v>0</v>
+        <v>532.5</v>
       </c>
     </row>
     <row r="31">
@@ -1288,7 +1288,7 @@
       </c>
       <c r="B31" s="9" t="inlineStr">
         <is>
-          <t>FIX DERMA SCAR GEL FOR SCAR 15ML SYNERRV</t>
+          <t>FIX DERMA MOISTURIZING CREAM FOR DRY SKIN 60G SYNERRV</t>
         </is>
       </c>
       <c r="C31" s="8" t="inlineStr">
@@ -1320,7 +1320,7 @@
       </c>
       <c r="B32" s="6" t="inlineStr">
         <is>
-          <t>ENTEROGERMINA 2BCFU ORAL SUSPENSION 5ML OPELLA HEALTHCARE</t>
+          <t>FIX DERMA SCAR GEL FOR SCAR 15ML SYNERRV</t>
         </is>
       </c>
       <c r="C32" s="5" t="inlineStr">
@@ -1330,20 +1330,20 @@
       </c>
       <c r="D32" s="5" t="inlineStr">
         <is>
-          <t>BOX</t>
+          <t>TUBE</t>
         </is>
       </c>
       <c r="E32" s="5" t="n">
         <v>0</v>
       </c>
       <c r="F32" s="5" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="G32" s="7" t="n">
-        <v>77.7</v>
+        <v>0</v>
       </c>
       <c r="H32" s="7" t="n">
-        <v>777</v>
+        <v>0</v>
       </c>
     </row>
     <row r="33">
@@ -1352,7 +1352,7 @@
       </c>
       <c r="B33" s="9" t="inlineStr">
         <is>
-          <t>INJ GARASENT (GENTAMICIN SULPHATE  80MG/2ML AMP) DUOPHARMA</t>
+          <t>ENTEROGERMINA 2BCFU ORAL SUSPENSION 5ML OPELLA HEALTHCARE</t>
         </is>
       </c>
       <c r="C33" s="8" t="inlineStr">
@@ -1362,7 +1362,7 @@
       </c>
       <c r="D33" s="8" t="inlineStr">
         <is>
-          <t>AMPULE</t>
+          <t>BOX</t>
         </is>
       </c>
       <c r="E33" s="8" t="n">
@@ -1372,10 +1372,10 @@
         <v>10</v>
       </c>
       <c r="G33" s="10" t="n">
-        <v>2.35</v>
+        <v>77.7</v>
       </c>
       <c r="H33" s="10" t="n">
-        <v>23.5</v>
+        <v>777</v>
       </c>
     </row>
     <row r="34">
@@ -1384,7 +1384,7 @@
       </c>
       <c r="B34" s="6" t="inlineStr">
         <is>
-          <t>CAP ESSENTIALSE MAX 600MG 30'S A.NATTERMANN &amp; CIE. GMBH</t>
+          <t>INJ GARASENT (GENTAMICIN SULPHATE  80MG/2ML AMP) DUOPHARMA</t>
         </is>
       </c>
       <c r="C34" s="5" t="inlineStr">
@@ -1394,20 +1394,20 @@
       </c>
       <c r="D34" s="5" t="inlineStr">
         <is>
-          <t>BOTTLE</t>
+          <t>AMPULE</t>
         </is>
       </c>
       <c r="E34" s="5" t="n">
         <v>0</v>
       </c>
       <c r="F34" s="5" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="G34" s="7" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="H34" s="7" t="n">
-        <v>0</v>
+        <v>23.5</v>
       </c>
     </row>
     <row r="35">
@@ -1416,7 +1416,7 @@
       </c>
       <c r="B35" s="9" t="inlineStr">
         <is>
-          <t>EPIFLOR YOGURT POWDER WITH PROBIOTICS 2GX30 SACHETS MD PHARMA SDN BHD</t>
+          <t>CAP ESSENTIALSE MAX 600MG 30'S A.NATTERMANN &amp; CIE. GMBH</t>
         </is>
       </c>
       <c r="C35" s="8" t="inlineStr">
@@ -1426,14 +1426,14 @@
       </c>
       <c r="D35" s="8" t="inlineStr">
         <is>
-          <t>BOX</t>
+          <t>BOTTLE</t>
         </is>
       </c>
       <c r="E35" s="8" t="n">
         <v>0</v>
       </c>
       <c r="F35" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G35" s="10" t="n">
         <v>0</v>
@@ -1448,7 +1448,7 @@
       </c>
       <c r="B36" s="6" t="inlineStr">
         <is>
-          <t>TAB IXIME ( CEFIXIME ) 400MG LUPIN</t>
+          <t>EPIFLOR YOGURT POWDER WITH PROBIOTICS 2GX30 SACHETS MD PHARMA SDN BHD</t>
         </is>
       </c>
       <c r="C36" s="5" t="inlineStr">
@@ -1458,14 +1458,14 @@
       </c>
       <c r="D36" s="5" t="inlineStr">
         <is>
-          <t>TABLET</t>
+          <t>BOX</t>
         </is>
       </c>
       <c r="E36" s="5" t="n">
         <v>0</v>
       </c>
       <c r="F36" s="5" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="G36" s="7" t="n">
         <v>0</v>
@@ -1480,7 +1480,7 @@
       </c>
       <c r="B37" s="9" t="inlineStr">
         <is>
-          <t>TAB DEXALONE ( DEXAMETHASONE ) 0.5MG DUOPHARMA</t>
+          <t>TAB IXIME ( CEFIXIME ) 400MG LUPIN</t>
         </is>
       </c>
       <c r="C37" s="8" t="inlineStr">
@@ -1494,16 +1494,16 @@
         </is>
       </c>
       <c r="E37" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F37" s="8" t="n">
         <v>10</v>
       </c>
-      <c r="F37" s="8" t="n">
-        <v>90</v>
-      </c>
       <c r="G37" s="10" t="n">
-        <v>0.08</v>
+        <v>0</v>
       </c>
       <c r="H37" s="10" t="n">
-        <v>7.2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="38">
@@ -1512,7 +1512,7 @@
       </c>
       <c r="B38" s="6" t="inlineStr">
         <is>
-          <t>INJ METHYCOBAL (MECOBALAMIN B12) 500MCG 1ML VIAL EISAI</t>
+          <t>TAB DEXALONE ( DEXAMETHASONE ) 0.5MG DUOPHARMA</t>
         </is>
       </c>
       <c r="C38" s="5" t="inlineStr">
@@ -1522,20 +1522,20 @@
       </c>
       <c r="D38" s="5" t="inlineStr">
         <is>
-          <t>VIAL</t>
+          <t>TABLET</t>
         </is>
       </c>
       <c r="E38" s="5" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="F38" s="5" t="n">
-        <v>9</v>
+        <v>90</v>
       </c>
       <c r="G38" s="7" t="n">
-        <v>6.8</v>
+        <v>0.08</v>
       </c>
       <c r="H38" s="7" t="n">
-        <v>61.2</v>
+        <v>7.2</v>
       </c>
     </row>
     <row r="39">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="B39" s="9" t="inlineStr">
         <is>
-          <t>INJ MALON ( METOCLOPRAMIDE ) 10MG/2ML DUOPHARMA</t>
+          <t>INJ METHYCOBAL (MECOBALAMIN B12) 500MCG 1ML VIAL EISAI</t>
         </is>
       </c>
       <c r="C39" s="8" t="inlineStr">
@@ -1558,16 +1558,16 @@
         </is>
       </c>
       <c r="E39" s="8" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="F39" s="8" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="G39" s="10" t="n">
-        <v>2.14</v>
+        <v>6.8</v>
       </c>
       <c r="H39" s="10" t="n">
-        <v>10.7</v>
+        <v>61.2</v>
       </c>
     </row>
     <row r="40">
@@ -1576,7 +1576,7 @@
       </c>
       <c r="B40" s="6" t="inlineStr">
         <is>
-          <t>TAB GOUTRIC ( FEBUXOSTAT) NOVUGEN</t>
+          <t>INJ MALON ( METOCLOPRAMIDE ) 10MG/2ML DUOPHARMA</t>
         </is>
       </c>
       <c r="C40" s="5" t="inlineStr">
@@ -1586,20 +1586,20 @@
       </c>
       <c r="D40" s="5" t="inlineStr">
         <is>
-          <t>TABLET</t>
+          <t>VIAL</t>
         </is>
       </c>
       <c r="E40" s="5" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="F40" s="5" t="n">
         <v>5</v>
       </c>
       <c r="G40" s="7" t="n">
-        <v>4.74</v>
+        <v>2.14</v>
       </c>
       <c r="H40" s="7" t="n">
-        <v>23.7</v>
+        <v>10.7</v>
       </c>
     </row>
     <row r="41">
@@ -1608,7 +1608,7 @@
       </c>
       <c r="B41" s="9" t="inlineStr">
         <is>
-          <t>S/C MOUNJARO (TIRZEPATIDE 25MG/ML) 2.5MG DOSE LILLY</t>
+          <t>TAB GOUTRIC ( FEBUXOSTAT) NOVUGEN</t>
         </is>
       </c>
       <c r="C41" s="8" t="inlineStr">
@@ -1618,20 +1618,20 @@
       </c>
       <c r="D41" s="8" t="inlineStr">
         <is>
-          <t>DOSE</t>
+          <t>TABLET</t>
         </is>
       </c>
       <c r="E41" s="8" t="n">
-        <v>11.5</v>
+        <v>10</v>
       </c>
       <c r="F41" s="8" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="G41" s="10" t="n">
-        <v>103.67</v>
+        <v>4.74</v>
       </c>
       <c r="H41" s="10" t="n">
-        <v>1347.71</v>
+        <v>23.7</v>
       </c>
     </row>
     <row r="42">
@@ -1640,7 +1640,7 @@
       </c>
       <c r="B42" s="6" t="inlineStr">
         <is>
-          <t>TAB NP PREDNISOLONE 5MG NORIPHARMA</t>
+          <t>S/C MOUNJARO (TIRZEPATIDE 25MG/ML) 2.5MG DOSE LILLY</t>
         </is>
       </c>
       <c r="C42" s="5" t="inlineStr">
@@ -1650,20 +1650,20 @@
       </c>
       <c r="D42" s="5" t="inlineStr">
         <is>
-          <t>TABLET</t>
+          <t>DOSE</t>
         </is>
       </c>
       <c r="E42" s="5" t="n">
-        <v>80</v>
+        <v>11.5</v>
       </c>
       <c r="F42" s="5" t="n">
-        <v>44</v>
+        <v>13</v>
       </c>
       <c r="G42" s="7" t="n">
-        <v>0.07000000000000001</v>
+        <v>103.67</v>
       </c>
       <c r="H42" s="7" t="n">
-        <v>3.08</v>
+        <v>1347.71</v>
       </c>
     </row>
     <row r="43">
@@ -1672,7 +1672,7 @@
       </c>
       <c r="B43" s="9" t="inlineStr">
         <is>
-          <t>TAB CLARINASE (PSEUDOEPHEDRINE 120MG, LORATADINE 5MG) BAYER</t>
+          <t>TAB NP PREDNISOLONE 5MG NORIPHARMA</t>
         </is>
       </c>
       <c r="C43" s="8" t="inlineStr">
@@ -1686,16 +1686,16 @@
         </is>
       </c>
       <c r="E43" s="8" t="n">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="F43" s="8" t="n">
-        <v>200</v>
+        <v>44</v>
       </c>
       <c r="G43" s="10" t="n">
-        <v>1.81</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="H43" s="10" t="n">
-        <v>362</v>
+        <v>3.08</v>
       </c>
     </row>
     <row r="44">
@@ -1704,7 +1704,7 @@
       </c>
       <c r="B44" s="6" t="inlineStr">
         <is>
-          <t>CHEWABLE SIMCONE ( SIMETICONE ) 80MG IMEKS</t>
+          <t>TAB CLARINASE (PSEUDOEPHEDRINE 120MG, LORATADINE 5MG) BAYER</t>
         </is>
       </c>
       <c r="C44" s="5" t="inlineStr">
@@ -1718,16 +1718,16 @@
         </is>
       </c>
       <c r="E44" s="5" t="n">
-        <v>130</v>
+        <v>100</v>
       </c>
       <c r="F44" s="5" t="n">
-        <v>70</v>
+        <v>200</v>
       </c>
       <c r="G44" s="7" t="n">
-        <v>0.16</v>
+        <v>1.81</v>
       </c>
       <c r="H44" s="7" t="n">
-        <v>11.2</v>
+        <v>362</v>
       </c>
     </row>
     <row r="45">
@@ -1736,7 +1736,7 @@
       </c>
       <c r="B45" s="9" t="inlineStr">
         <is>
-          <t>TAB SHINTAMET (CIMETIDINE) 400MG Y.S.P.</t>
+          <t>CHEWABLE SIMCONE ( SIMETICONE ) 80MG IMEKS</t>
         </is>
       </c>
       <c r="C45" s="8" t="inlineStr">
@@ -1750,16 +1750,16 @@
         </is>
       </c>
       <c r="E45" s="8" t="n">
-        <v>20</v>
+        <v>130</v>
       </c>
       <c r="F45" s="8" t="n">
-        <v>180</v>
+        <v>70</v>
       </c>
       <c r="G45" s="10" t="n">
-        <v>0.58</v>
+        <v>0.16</v>
       </c>
       <c r="H45" s="10" t="n">
-        <v>104.4</v>
+        <v>11.2</v>
       </c>
     </row>
     <row r="46">
@@ -1768,7 +1768,7 @@
       </c>
       <c r="B46" s="6" t="inlineStr">
         <is>
-          <t>SYR BUCANIL (TERBUTALINE SULPHATE 1.5MG/5ML) 100ML Y.S.P.</t>
+          <t>TAB SHINTAMET (CIMETIDINE) 400MG Y.S.P.</t>
         </is>
       </c>
       <c r="C46" s="5" t="inlineStr">
@@ -1778,20 +1778,20 @@
       </c>
       <c r="D46" s="5" t="inlineStr">
         <is>
-          <t>BOTTLE</t>
+          <t>TABLET</t>
         </is>
       </c>
       <c r="E46" s="5" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="F46" s="5" t="n">
-        <v>20</v>
+        <v>180</v>
       </c>
       <c r="G46" s="7" t="n">
-        <v>3.7</v>
+        <v>0.58</v>
       </c>
       <c r="H46" s="7" t="n">
-        <v>74</v>
+        <v>104.4</v>
       </c>
     </row>
     <row r="47">
@@ -1800,7 +1800,7 @@
       </c>
       <c r="B47" s="9" t="inlineStr">
         <is>
-          <t>TAB BETASERC (BETAHISTINE) 24MG ABBOTT</t>
+          <t>SYR BUCANIL (TERBUTALINE SULPHATE 1.5MG/5ML) 100ML Y.S.P.</t>
         </is>
       </c>
       <c r="C47" s="8" t="inlineStr">
@@ -1810,20 +1810,20 @@
       </c>
       <c r="D47" s="8" t="inlineStr">
         <is>
-          <t>TABLET</t>
+          <t>BOTTLE</t>
         </is>
       </c>
       <c r="E47" s="8" t="n">
         <v>10</v>
       </c>
       <c r="F47" s="8" t="n">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="G47" s="10" t="n">
-        <v>1.62</v>
+        <v>3.7</v>
       </c>
       <c r="H47" s="10" t="n">
-        <v>64.8</v>
+        <v>74</v>
       </c>
     </row>
     <row r="48">
@@ -1832,7 +1832,7 @@
       </c>
       <c r="B48" s="6" t="inlineStr">
         <is>
-          <t>TAB CONCOR (BISOPROLOL) 5MG MERCKS</t>
+          <t>TAB BETASERC (BETAHISTINE) 24MG ABBOTT</t>
         </is>
       </c>
       <c r="C48" s="5" t="inlineStr">
@@ -1849,13 +1849,13 @@
         <v>10</v>
       </c>
       <c r="F48" s="5" t="n">
-        <v>290</v>
+        <v>40</v>
       </c>
       <c r="G48" s="7" t="n">
-        <v>1.53</v>
+        <v>1.62</v>
       </c>
       <c r="H48" s="7" t="n">
-        <v>443.7</v>
+        <v>64.8</v>
       </c>
     </row>
     <row r="49">
@@ -1864,7 +1864,7 @@
       </c>
       <c r="B49" s="9" t="inlineStr">
         <is>
-          <t>SMECTA (DIOSMECTITE 3G) ORANGE-VANILLA POWDER SACHETS ZUELLIG</t>
+          <t>TAB CONCOR (BISOPROLOL) 5MG MERCKS</t>
         </is>
       </c>
       <c r="C49" s="8" t="inlineStr">
@@ -1874,20 +1874,20 @@
       </c>
       <c r="D49" s="8" t="inlineStr">
         <is>
-          <t>SACHET</t>
+          <t>TABLET</t>
         </is>
       </c>
       <c r="E49" s="8" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="F49" s="8" t="n">
-        <v>88</v>
+        <v>290</v>
       </c>
       <c r="G49" s="10" t="n">
-        <v>1.66</v>
+        <v>1.53</v>
       </c>
       <c r="H49" s="10" t="n">
-        <v>146.08</v>
+        <v>443.7</v>
       </c>
     </row>
     <row r="50">
@@ -1896,7 +1896,7 @@
       </c>
       <c r="B50" s="6" t="inlineStr">
         <is>
-          <t>TAB VELOXIN (MECLOZINE 25MG/PYRIDOXINE 50MG) PHARM-D</t>
+          <t>SMECTA (DIOSMECTITE 3G) ORANGE-VANILLA POWDER SACHETS ZUELLIG</t>
         </is>
       </c>
       <c r="C50" s="5" t="inlineStr">
@@ -1906,20 +1906,20 @@
       </c>
       <c r="D50" s="5" t="inlineStr">
         <is>
-          <t>TABLET</t>
+          <t>SACHET</t>
         </is>
       </c>
       <c r="E50" s="5" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="F50" s="5" t="n">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="G50" s="7" t="n">
-        <v>1.06</v>
+        <v>1.66</v>
       </c>
       <c r="H50" s="7" t="n">
-        <v>95.40000000000001</v>
+        <v>146.08</v>
       </c>
     </row>
     <row r="51">
@@ -1928,7 +1928,7 @@
       </c>
       <c r="B51" s="9" t="inlineStr">
         <is>
-          <t>TAB STORVAS C (ATORVASTATIN) 20MG RANBAXY</t>
+          <t>TAB VELOXIN (MECLOZINE 25MG/PYRIDOXINE 50MG) PHARM-D</t>
         </is>
       </c>
       <c r="C51" s="8" t="inlineStr">
@@ -1942,16 +1942,16 @@
         </is>
       </c>
       <c r="E51" s="8" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="F51" s="8" t="n">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="G51" s="10" t="n">
-        <v>0.68</v>
+        <v>1.06</v>
       </c>
       <c r="H51" s="10" t="n">
-        <v>54.4</v>
+        <v>95.40000000000001</v>
       </c>
     </row>
     <row r="52">
@@ -1960,7 +1960,7 @@
       </c>
       <c r="B52" s="6" t="inlineStr">
         <is>
-          <t>TAB DIAPO (DIAZEPAM) 5MG DUOPHARMA</t>
+          <t>TAB STORVAS C (ATORVASTATIN) 20MG RANBAXY</t>
         </is>
       </c>
       <c r="C52" s="5" t="inlineStr">
@@ -1974,16 +1974,16 @@
         </is>
       </c>
       <c r="E52" s="5" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="F52" s="5" t="n">
-        <v>40</v>
+        <v>80</v>
       </c>
       <c r="G52" s="7" t="n">
-        <v>1.44</v>
+        <v>0.68</v>
       </c>
       <c r="H52" s="7" t="n">
-        <v>57.6</v>
+        <v>54.4</v>
       </c>
     </row>
     <row r="53">
@@ -1992,7 +1992,7 @@
       </c>
       <c r="B53" s="9" t="inlineStr">
         <is>
-          <t>TAB ZITHROMAX (AZITHROMYCIN) 250MG 6'S PFIZER</t>
+          <t>TAB DIAPO (DIAZEPAM) 5MG DUOPHARMA</t>
         </is>
       </c>
       <c r="C53" s="8" t="inlineStr">
@@ -2002,20 +2002,20 @@
       </c>
       <c r="D53" s="8" t="inlineStr">
         <is>
-          <t>PACKET</t>
+          <t>TABLET</t>
         </is>
       </c>
       <c r="E53" s="8" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="F53" s="8" t="n">
-        <v>59</v>
+        <v>40</v>
       </c>
       <c r="G53" s="10" t="n">
-        <v>42.4</v>
+        <v>1.44</v>
       </c>
       <c r="H53" s="10" t="n">
-        <v>2501.6</v>
+        <v>57.6</v>
       </c>
     </row>
     <row r="54">
@@ -2985,7 +2985,7 @@
         </is>
       </c>
       <c r="H84" s="12" t="n">
-        <v>13962</v>
+        <v>14004.4</v>
       </c>
     </row>
     <row r="86">
@@ -2998,7 +2998,7 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Generated: 2026-06-18 17:28</t>
+          <t>Generated: 2026-06-18 17:31</t>
         </is>
       </c>
     </row>
